--- a/Result/checksun_type/元件裝置.xlsx
+++ b/Result/checksun_type/元件裝置.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>64.98</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>70.57</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>77.91</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>70.56999999999999</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>77.91</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>14440.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>20248.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>20248</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>24342.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>83648.54</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>83648.53999999999</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-6498.399258858575</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>14440</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>14440.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>64.64</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>71.36</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>78.17</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>71.36</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>78.17</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>24071.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>21063.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>21063.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>24973.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>87968.22</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>87968.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-6448.589263125443</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>24071</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>24071.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>64.67999999999999</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>72.1</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>78.45</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>78.45</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>32330.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>20817.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>20817.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>25696.4</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>88580.28</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>88580.28</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-7179.018224109343</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>32330</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>32330.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>65.34</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>73.04</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>78.72</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>73.04000000000001</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>78.72</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>19890.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>23556.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>23556.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>24414.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>88503.74</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>88503.74000000001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-8850.987517511006</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>19890</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>19890.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>66.6</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>73.96</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>79.03</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>73.95999999999999</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>79.03</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>10509.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>27228.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>27228.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>24641.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>88926.62</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>88926.62</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-9590.551239602271</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>10509</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>10509.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>67.8</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>74.79</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>79.26</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>74.79000000000001</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>79.26000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>18519.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>28437.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>28437</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>26764.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>89466.98</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>89466.98</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-9299.444012604003</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>18519</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>18519.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>69.32000000000001</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>75.59</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>79.5</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>75.59</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>79.5</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>22838.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>28883.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>28883.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>29999.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>89926.84</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>89926.84</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-9409.667830727769</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>22838</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>22838.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>70.36</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>76.29</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>79.75</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>76.29000000000001</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>79.75</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>46028.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>30575.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>30575.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>30583.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>91090.28</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>91090.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-9693.820862664295</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>46028</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>46028.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>71.60000000000001</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>77.02</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>79.98</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>77.02</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>79.98</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>38250.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>25273.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>25273</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>28352.7</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>93285.46</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>93285.46000000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-12238.18873462132</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>38250</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>38250.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>72.28</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>77.65</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>80.06</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>80.06</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>16550.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>22053.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>22053.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>31261.5</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>92957.46</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>92957.46000000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-14602.56466832346</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>16550</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>16550.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>72.72</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>78.16</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>80.11</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>78.16</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>80.11</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>20750.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>25092.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>25092</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>34192.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>93074.84</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>93074.84</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-15133.72440688638</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>20750</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>20750.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>245.9</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>282.15</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>286.24</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>282.15</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>286.24</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>181496538.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>248712009.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>248712009.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>295583263.9</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>404415989.88</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>404415989.88</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-36865543.57806414</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>181496538</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>181496538.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>243.7</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>286.4</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>287.62</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>286.4</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>287.62</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>326035900.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>303753353.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>303753353.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>308503858.9</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>444892029.6</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>444892029.6</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-31426505.93227613</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>326035900</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>326035900.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>242.9</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>290.23</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>288.95</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>290.23</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>288.95</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>131381608.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>344648291.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>344648291.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>305244759.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>486354631.84</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>486354631.84</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-38020437.15499777</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>131381608</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>131381608.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>248.1</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>294.2</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>289.92</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>294.2</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>289.92</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>191628215.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>361404158.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>361404158.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>314017182.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>492826395.88</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>492826395.88</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-25226649.14620733</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>191628215</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>191628215.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>255.9</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>297.35</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>290.45</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>297.35</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>290.45</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>413017787.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>370339106.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>370339106.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>343302605.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>491927087.64</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>491927087.64</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-12503850.98557067</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>413017787</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>413017787.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>262.8</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>299.42</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>290.68</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>299.42</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>290.68</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>456703259.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>342454518.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>342454518.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>329501632.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>487045635.88</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>487045635.88</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-17602170.22089082</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>456703259</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>456703259.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>271.1</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>302.12</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>291.04</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>302.12</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>291.04</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>530510587.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>313254364.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>313254364</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>318010950.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>482171320.06</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>482171320.06</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-28937420.76345921</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>530510587</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>530510587.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>279.8</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>304.35</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>291.39</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>304.35</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>291.39</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>215160943.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>265841228.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>265841228.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>296018261.7</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>474035134.12</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>474035134.12</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-52005084.51129037</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>215160943</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>215160943.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>285.6</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>305.35</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>291.28</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>305.35</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>291.28</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>236302957.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>266630206.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>266630206.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>300487017.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>472138847.46</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>472138847.46</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-49314103.56136036</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>236302957</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>236302957.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>290.8</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>306.1</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>291.06</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>306.1</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>291.06</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>273594845.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>316266104.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>316266104.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>321700457.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>472162353.72</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>472162353.72</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-45973842.86284024</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>273594845</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>273594845.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>298.5</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>306.35</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>290.96</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>306.35</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>290.96</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>310702488.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>316548746.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>316548746</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>396274780.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>469508914.58</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>469508914.58</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-43555678.33413863</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>310702488</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>310702488.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>21.39</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>22.32</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>21.54</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>21.54</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>75835085.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>74556049.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>74556049.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>107350647.0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>155769097.24</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>155769097.24</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-19021459.724145</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>75835085</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>75835085.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>21.18</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>22.48</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>21.48</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>21.48</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>176746147.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>69470289.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>69470289</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>114955587.1</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>155048753.2</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>155048753.2</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-19584071.56791055</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>176746147</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>176746147.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>21.06</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>22.63</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>21.4</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>22117198.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>43595395.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>43595395.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>112406534.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>151879732.8</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>151879732.8</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-30500271.14586455</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>22117198</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>22117198.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>21.4</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>21.37</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>21.37</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>47493105.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>60904246.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>60904246.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>132547985.0</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>151644707.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>151644707</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-28438159.18058938</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>47493105</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>47493105.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>21.9</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>23.09</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>21.34</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>23.09</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>21.34</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>50588711.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>69376955.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>69376955</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>135412851.8</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>150938400.98</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>150938400.98</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-27195483.58088952</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>50588711</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>50588711.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>22.57</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>23.28</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>21.29</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>21.29</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>50406284.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>140145244.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>140145244.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>134841933.4</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>150124983.38</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>150124983.38</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-24780637.52485795</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>50406284</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>50406284.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>22.99</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>23.35</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>21.24</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>21.24</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>47371679.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>160440885.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>160440885.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>133609829.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>149378068.98</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>149378068.98</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-20426288.92606792</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>47371679</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>47371679.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>22.99</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>23.32</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>21.16</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>21.16</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>108661455.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>181217673.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>181217673.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>136054852.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>148673712.48</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>148673712.48</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-13151144.35900834</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>108661455</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>108661455.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>23.31</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>23.26</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>21.09</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>21.09</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>89856646.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>204191723.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>204191723.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>131856533.2</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>146868110.92</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>146868110.92</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-8855158.678958625</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>89856646</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>89856646.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>23.13</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>23.21</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>21</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>404430160.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>201448748.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>201448748.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>133986736.8</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>145510316.32</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>145510316.32</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-386979.6474962234</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>404430160</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>404430160.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>23.04</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>20.9</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>151884486.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>129538622.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>129538622</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>108795424.1</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>138556413.9</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>138556413.9</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-21980065.40085366</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>151884486</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>151884486.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/元件裝置.xlsx
+++ b/Result/checksun_type/元件裝置.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW34"/>
+  <dimension ref="A1:CW31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-25.91</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-20.49</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,66 +1144,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>59.65</t>
+          <t>34.37</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.34</v>
+        <v>-0.55</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.25</v>
+        <v>-0.82</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>64.97999999999999</t>
+          <t>65.06</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>65.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="BA2" t="n">
-        <v>71.20999999999999</v>
+        <v>70.48</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>74.93</t>
+          <t>74.67</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-1.51</v>
+        <v>-1.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>-1.91</v>
+        <v>-1.74</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-132.58</t>
+          <t>-129.61</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>156752.2959610028</t>
+          <t>156350.4854166667</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>5683.0</t>
+          <t>8460.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>6088</v>
+        <v>7260.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>8217.1</t>
+          <t>7307.0</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>38427.3</v>
+        <v>27036.72</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-2129</t>
+          <t>-46</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-3245.763148995786</t>
+          <t>-2853.066322941873</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-2271.619577797707</t>
+          <t>-1731.759903065828</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>5683.0</t>
+          <t>8460.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>50.15</t>
+          <t>49.82</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-19.63</t>
+          <t>-21.22</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>54.39</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.73</v>
+        <v>-0.55</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.6</v>
+        <v>-1.13</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>64.78</t>
+          <t>64.96000000000001</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>65.83</v>
+        <v>65.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>71.76000000000001</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>75.05</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-1.62</v>
+        <v>-1.46</v>
       </c>
       <c r="BE3" t="n">
-        <v>-2.01</v>
+        <v>-1.82</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-134.28</t>
+          <t>-131.05</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>156752.2959610028</t>
+          <t>156350.4854166667</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>8905.0</t>
+          <t>7674.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>7734.2</v>
+        <v>6839</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>8324.3</t>
+          <t>7600.3</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>45008.82</v>
+        <v>29167.7</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-590</t>
+          <t>-761</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-3422.880161940891</t>
+          <t>-3056.94021746479</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-2338.890998238354</t>
+          <t>-2018.414094044312</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>8905.0</t>
+          <t>7674.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>50.15</t>
+          <t>49.82</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-30.51</t>
+          <t>-25.91</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-20.49</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>59.65</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="AV4" t="n">
-        <v>-1.53</v>
+        <v>-1.25</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>64.74000000000001</t>
+          <t>64.97999999999999</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>65.73999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>72.20999999999999</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>75.17</t>
+          <t>74.93</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>20.81</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-1.8</v>
+        <v>-1.51</v>
       </c>
       <c r="BE4" t="n">
-        <v>-2.11</v>
+        <v>-1.91</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-135.95</t>
+          <t>-132.58</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>156752.2959610028</t>
+          <t>156350.4854166667</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>5581.0</t>
+          <t>5683.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>6958.2</v>
+        <v>6088</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>10013.0</t>
+          <t>8217.1</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>47876.18</v>
+        <v>38427.3</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-3054</t>
+          <t>-2129</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-3619.969100795898</t>
+          <t>-3245.763148995786</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-2696.675491787904</t>
+          <t>-2271.619577797707</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>5581.0</t>
+          <t>5683.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>50.15</t>
+          <t>49.82</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-37.03</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-21.71</t>
+          <t>-19.63</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.2</v>
+        <v>1.73</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.99</v>
+        <v>-1.6</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>64.97999999999999</t>
+          <t>64.78</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>65.63</v>
+        <v>65.83</v>
       </c>
       <c r="BA5" t="n">
-        <v>72.72</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>75.29</t>
+          <t>75.05</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-1.9</v>
+        <v>-1.62</v>
       </c>
       <c r="BE5" t="n">
-        <v>-2.19</v>
+        <v>-2.01</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-137.29</t>
+          <t>-134.28</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>156752.2959610028</t>
+          <t>156350.4854166667</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>6352.0</t>
+          <t>8905.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>7353.4</v>
+        <v>7734.2</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>11678.4</t>
+          <t>8324.3</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>56215</v>
+        <v>45008.82</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-4325</t>
+          <t>-590</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-3787.840666070078</t>
+          <t>-3422.880161940891</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-2755.343500723411</t>
+          <t>-2338.890998238354</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>6352.0</t>
+          <t>8905.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>50.15</t>
+          <t>49.82</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-29.82</t>
+          <t>-30.51</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>20.61</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.77</v>
+        <v>0.25</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.77</v>
+        <v>-1.53</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>64.74000000000001</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>65.70999999999999</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="BA6" t="n">
-        <v>73.23999999999999</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.17</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-1.93</v>
+        <v>-1.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>-2.26</v>
+        <v>-2.11</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-138.52</t>
+          <t>-135.95</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>156752.2959610028</t>
+          <t>156350.4854166667</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>3919.0</t>
+          <t>5581.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>8361.6</v>
+        <v>6958.2</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>11914.5</t>
+          <t>10013.0</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>65773.17999999999</v>
+        <v>47876.18</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-3552</t>
+          <t>-3054</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-3975.567423405837</t>
+          <t>-3619.969100795898</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-2823.356959891156</t>
+          <t>-2696.675491787904</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>3919.0</t>
+          <t>5581.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>50.15</t>
+          <t>49.82</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-16.88</t>
+          <t>-37.03</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,12 +3579,12 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3594,51 +3594,51 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.47</v>
+        <v>-1.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.84</v>
+        <v>-0.99</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-9.75</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>65.16</t>
+          <t>64.97999999999999</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>65.72</v>
+        <v>65.63</v>
       </c>
       <c r="BA7" t="n">
-        <v>73.63</v>
+        <v>72.72</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>75.52</t>
+          <t>75.29</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-1.99</v>
+        <v>-1.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>-2.34</v>
+        <v>-2.19</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-139.93</t>
+          <t>-137.29</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>156752.2959610028</t>
+          <t>156350.4854166667</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>13914.0</t>
+          <t>6352.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>10346.2</v>
+        <v>7353.4</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>12448.0</t>
+          <t>11678.4</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>67956.56</v>
+        <v>56215</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-2101</t>
+          <t>-4325</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-4185.06023495396</t>
+          <t>-3787.840666070078</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-2559.006295848963</t>
+          <t>-2755.343500723411</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>13914.0</t>
+          <t>6352.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>50.15</t>
+          <t>49.82</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-29.82</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-19.88</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.52</v>
+        <v>-0.77</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.68</v>
+        <v>-0.77</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-11.07</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>65.35999999999999</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>65.8</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="BA8" t="n">
-        <v>74</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>75.63</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-1.99</v>
+        <v>-1.93</v>
       </c>
       <c r="BE8" t="n">
-        <v>-2.43</v>
+        <v>-2.26</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-141.43</t>
+          <t>-138.52</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>156752.2959610028</t>
+          <t>156350.4854166667</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>5025.0</t>
+          <t>3919.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>8914.4</v>
+        <v>8361.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>11661.9</t>
+          <t>11914.5</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>69399.5</v>
+        <v>65773.17999999999</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-2747</t>
+          <t>-3552</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-4480.706405700324</t>
+          <t>-3975.567423405837</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-3160.862265222655</t>
+          <t>-2823.356959891156</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>5025.0</t>
+          <t>3919.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>50.15</t>
+          <t>49.82</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>-16.88</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-19.39</t>
+          <t>-21.71</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>1.07</v>
+        <v>-1.47</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.75</v>
+        <v>-0.84</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-11.27</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>65.16</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>65.90000000000001</v>
+        <v>65.72</v>
       </c>
       <c r="BA9" t="n">
-        <v>74.26000000000001</v>
+        <v>73.63</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>75.72</t>
+          <t>75.52</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-2.11</v>
+        <v>-1.99</v>
       </c>
       <c r="BE9" t="n">
-        <v>-2.54</v>
+        <v>-2.34</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-143.31</t>
+          <t>-139.93</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>156752.2959610028</t>
+          <t>156350.4854166667</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>7557.0</t>
+          <t>13914.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>13067.8</v>
+        <v>10346.2</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>12234.8</t>
+          <t>12448.0</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>71028.42</v>
+        <v>67956.56</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>-2101</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-4720.678067605354</t>
+          <t>-4185.06023495396</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-2955.375711998546</t>
+          <t>-2559.006295848963</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>7557.0</t>
+          <t>13914.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4732,17 +4732,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>50.15</t>
+          <t>49.82</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>29.39</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-20.37</t>
+          <t>-19.88</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.18</v>
+        <v>0.52</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.93</v>
+        <v>-0.68</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-11.07</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>65.35999999999999</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>66.04000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>74.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.63</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-2.28</v>
+        <v>-1.99</v>
       </c>
       <c r="BE10" t="n">
-        <v>-2.65</v>
+        <v>-2.43</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-145.14</t>
+          <t>-141.43</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>156752.2959610028</t>
+          <t>156350.4854166667</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>11393.0</t>
+          <t>5025.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>16003.4</v>
+        <v>8914.4</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>12368.0</t>
+          <t>11661.9</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>71778.02</v>
+        <v>69399.5</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>-2747</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-5041.642132261138</t>
+          <t>-4480.706405700324</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-2827.5600748213</t>
+          <t>-3160.862265222655</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>11393.0</t>
+          <t>5025.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>50.15</t>
+          <t>49.82</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26.27</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-21.34</t>
+          <t>-19.39</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.61</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-1.98</v>
+        <v>1.07</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.84</v>
+        <v>-0.75</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-11.43</t>
+          <t>-11.27</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>66.36</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="BA11" t="n">
-        <v>74.92</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>75.87</t>
+          <t>75.72</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-2.37</v>
+        <v>-2.11</v>
       </c>
       <c r="BE11" t="n">
-        <v>-2.74</v>
+        <v>-2.54</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-146.71</t>
+          <t>-143.31</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>156752.2959610028</t>
+          <t>156350.4854166667</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>13842.0</t>
+          <t>7557.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>15467.4</v>
+        <v>13067.8</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>12249.1</t>
+          <t>12234.8</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>72529.10000000001</v>
+        <v>71028.42</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>833</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-5444.202506341108</t>
+          <t>-4720.678067605354</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-2954.982019038762</t>
+          <t>-2955.375711998546</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>13842.0</t>
+          <t>7557.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>50.15</t>
+          <t>49.82</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
+          <t>66.5</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
           <t>65.6</t>
         </is>
       </c>
-      <c r="CS11" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
-      </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5808,22 +5808,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>423.037</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>251.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>-46.78</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,37 +5863,37 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2025-10-07 00:00:00</t>
+          <t>2025-10-09 00:00:00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-10-15 00:00:00</t>
+          <t>2025-11-07 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-08-18 00:00:00</t>
+          <t>2025-09-10 00:00:00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-09-23 00:00:00</t>
+          <t>2025-09-19 00:00:00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>307.5</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>301.5</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>317.5</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-20.49</t>
+          <t>-16.58</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025/05/23</t>
+          <t>2025/10/01</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>278.0</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5943,67 +5943,67 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2025/11/10</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>251.0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025/07/08</t>
+          <t>2025/10/14</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>284.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025/10/15</t>
+          <t>2025/11/07</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>301.5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2025/09/23</t>
+          <t>2025/09/19</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-10-07 00:00:00</t>
+          <t>2025-10-29 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,121 +6014,121 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>53.26</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.84</v>
+        <v>0.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.5</v>
+        <v>0.42</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-8.45</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>66.42</t>
+          <t>250.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>66.76000000000001</v>
+        <v>249.45</v>
       </c>
       <c r="BA12" t="n">
-        <v>75.29000000000001</v>
+        <v>272.46</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>75.93</t>
+          <t>275.68</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-2.38</v>
+        <v>-4.69</v>
       </c>
       <c r="BE12" t="n">
-        <v>-2.83</v>
+        <v>-6.45</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-148.26</t>
+          <t>-131.28</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>156752.2959610028</t>
+          <t>574936848.40625</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>6755.0</t>
+          <t>105812909.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>14549.8</v>
+        <v>139308963.8</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>12308.9</t>
+          <t>261739219.4</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>74233.44</v>
+        <v>313158870.14</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>-122430255</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-5896.78804948699</t>
+          <t>-9118833.563071579</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-3293.871152955177</t>
+          <t>-23412670.15888375</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>6755.0</t>
+          <t>105812909.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6138,27 +6138,27 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>291.5</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/10/20</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-13.72</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>撼訊</t>
+          <t>華擎</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>撼訊</t>
+          <t>華擎</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
@@ -6168,32 +6168,32 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>-14.1596150519797</t>
+          <t>-26.86876387135273</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>49.21329002443228</t>
+          <t>21.34391693134842</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>74.45901000762517</t>
+          <t>93.90171918997666</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,87 +6203,87 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>94.25</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>7.80%</t>
+          <t>13.06%</t>
         </is>
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>5.37%</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>50.15</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>31074</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>顯示卡99.76%、工程建設0.20%、其他0.04% (2024年)</t>
+          <t>電腦周邊產品94.10%、其他5.90% (2024年)</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>撼訊-電腦及週邊設備業-上櫃</t>
+          <t>華擎-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業右上上市</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>249.5</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>252.5</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>251.5</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>79.39</t>
         </is>
       </c>
       <c r="CV12" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 顯示卡** 區塊鏈 - 元件裝置</t>
+          <t>** 電腦及週邊設備 - 主機板、顯示卡、工業電腦、伺服器** 區塊鏈 - 元件裝置</t>
         </is>
       </c>
       <c r="CW12" t="inlineStr">
@@ -6295,7 +6295,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>411.277</t>
+          <t>629.331</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>251.5</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-48.57</t>
+          <t>-49.80</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-16.58</t>
+          <t>-18.08</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>31.33</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>0.96</v>
+        <v>-1.12</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.26</v>
+        <v>0.13</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>249.1</t>
+          <t>249.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>249.75</v>
+        <v>249.48</v>
       </c>
       <c r="BA13" t="n">
-        <v>273.94</v>
+        <v>273.2</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>276.44</t>
+          <t>276.01</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-5.37</v>
+        <v>-5.22</v>
       </c>
       <c r="BE13" t="n">
-        <v>-7.31</v>
+        <v>-6.9</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-135.44</t>
+          <t>-133.42</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>575989895.6908078</t>
+          <t>574936848.40625</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>103728241.0</t>
+          <t>156710922.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>151174816</v>
+        <v>149692353.4</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>293940049.4</t>
+          <t>298173238.0</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>321773197.24</v>
+        <v>314265751.62</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-142765233</t>
+          <t>-148480884</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-4215445.001420825</t>
+          <t>-6519954.18201482</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-17936992.71030468</t>
+          <t>-19194754.67528179</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>103728241.0</t>
+          <t>156710922.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-13.72</t>
+          <t>-15.27</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
+          <t>253.0</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
           <t>254.0</t>
         </is>
       </c>
-      <c r="CR13" t="inlineStr">
-        <is>
-          <t>254.0</t>
-        </is>
-      </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>250.5</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>251.5</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>439.949</t>
+          <t>411.277</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>252.5</t>
+          <t>251.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-38.19</t>
+          <t>-48.57</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-16.25</t>
+          <t>-16.58</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>31.33</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>1.9</v>
+        <v>0.96</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.77</v>
+        <v>-0.26</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>247.8</t>
+          <t>249.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>249.72</v>
+        <v>249.75</v>
       </c>
       <c r="BA14" t="n">
-        <v>274.88</v>
+        <v>273.94</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>276.86</t>
+          <t>276.44</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-5.95</v>
+        <v>-5.37</v>
       </c>
       <c r="BE14" t="n">
-        <v>-7.8</v>
+        <v>-7.31</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-137.80</t>
+          <t>-135.44</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>575989895.6908078</t>
+          <t>574936848.40625</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>111041677.0</t>
+          <t>103728241.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>180118592.8</v>
+        <v>151174816</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>291402733.8</t>
+          <t>293940049.4</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>331500512.82</v>
+        <v>321773197.24</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-111284141</t>
+          <t>-142765233</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-1720618.145260124</t>
+          <t>-4215445.001420825</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-9822867.19925499</t>
+          <t>-17936992.71030468</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>111041677.0</t>
+          <t>103728241.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-13.72</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>253.0</t>
+          <t>254.0</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>255.0</t>
+          <t>254.0</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>252.5</t>
+          <t>251.5</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>877.585</t>
+          <t>439.949</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>252.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-22.93</t>
+          <t>-38.19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-16.25</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="AV15" t="n">
-        <v>-1.21</v>
+        <v>-0.77</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>247.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>249.12</v>
+        <v>249.72</v>
       </c>
       <c r="BA15" t="n">
-        <v>275.98</v>
+        <v>274.88</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>277.17</t>
+          <t>276.86</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-6.69</v>
+        <v>-5.95</v>
       </c>
       <c r="BE15" t="n">
-        <v>-8.26</v>
+        <v>-7.8</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-140.04</t>
+          <t>-137.80</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>575989895.6908078</t>
+          <t>574936848.40625</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>219251070.0</t>
+          <t>111041677.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>222513395</v>
+        <v>180118592.8</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>288714631.4</t>
+          <t>291402733.8</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>354780331.98</v>
+        <v>331500512.82</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-66201236</t>
+          <t>-111284141</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-247481.9536246935</t>
+          <t>-1720618.145260124</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>1335974.930789322</t>
+          <t>-9822867.19925499</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>219251070.0</t>
+          <t>111041677.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>253.0</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
+          <t>255.0</t>
+        </is>
+      </c>
+      <c r="CS15" t="inlineStr">
+        <is>
+          <t>250.5</t>
+        </is>
+      </c>
+      <c r="CT15" t="inlineStr">
+        <is>
           <t>252.5</t>
-        </is>
-      </c>
-      <c r="CS15" t="inlineStr">
-        <is>
-          <t>247.0</t>
-        </is>
-      </c>
-      <c r="CT15" t="inlineStr">
-        <is>
-          <t>250.0</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>641.295</t>
+          <t>877.585</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>37.40</t>
+          <t>-22.93</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-17.74</t>
+          <t>-17.08</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>14.67</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>0.57</v>
+        <v>1.58</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.74</v>
+        <v>-1.21</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-10.23</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>246.6</t>
+          <t>246.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>248.45</v>
+        <v>249.12</v>
       </c>
       <c r="BA16" t="n">
-        <v>276.77</v>
+        <v>275.98</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>277.44</t>
+          <t>277.17</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-7.29</v>
+        <v>-6.69</v>
       </c>
       <c r="BE16" t="n">
-        <v>-8.66</v>
+        <v>-8.26</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-141.95</t>
+          <t>-140.04</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>575989895.6908078</t>
+          <t>574936848.40625</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>157729857.0</t>
+          <t>219251070.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>384169475</v>
+        <v>222513395</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>279606210.2</t>
+          <t>288714631.4</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>357070115.46</v>
+        <v>354780331.98</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>104563264</t>
+          <t>-66201236</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-535383.2053363327</t>
+          <t>-247481.9536246935</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>5635601.047610193</t>
+          <t>1335974.930789322</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>157729857.0</t>
+          <t>219251070.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-14.92</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,17 +8141,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.5</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>242.5</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8243,7 +8243,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>665.072</t>
+          <t>641.295</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>243.5</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>64.69</t>
+          <t>37.40</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-19.24</t>
+          <t>-17.74</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-2.87</v>
+        <v>0.57</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.89</v>
+        <v>-0.74</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-10.23</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>250.7</t>
+          <t>246.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>248.5</v>
+        <v>248.45</v>
       </c>
       <c r="BA17" t="n">
-        <v>277.45</v>
+        <v>276.77</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>277.78</t>
+          <t>277.44</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-7.75</v>
+        <v>-7.29</v>
       </c>
       <c r="BE17" t="n">
-        <v>-9</v>
+        <v>-8.66</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-143.60</t>
+          <t>-141.95</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>575989895.6908078</t>
+          <t>574936848.40625</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>164123235.0</t>
+          <t>157729857.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>446654122.6</v>
+        <v>384169475</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>271212851.0</t>
+          <t>279606210.2</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>366042163</v>
+        <v>357070115.46</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>175441271</t>
+          <t>104563264</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-1657380.342235701</t>
+          <t>-535383.2053363327</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>18168211.14136815</t>
+          <t>5635601.047610193</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>164123235.0</t>
+          <t>157729857.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-16.47</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,17 +8628,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
           <t>248.0</t>
         </is>
       </c>
-      <c r="CR17" t="inlineStr">
-        <is>
-          <t>251.0</t>
-        </is>
-      </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>243.5</t>
+          <t>242.5</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>243.5</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1014.014</t>
+          <t>665.072</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>245.0</t>
+          <t>243.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>67.84</t>
+          <t>64.69</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-18.74</t>
+          <t>-19.24</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-2.35</v>
+        <v>-2.87</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-10.64</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>250.9</t>
+          <t>250.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>248.4</v>
+        <v>248.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>277.99</v>
+        <v>277.45</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>278.21</t>
+          <t>277.78</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-7.76</v>
+        <v>-7.75</v>
       </c>
       <c r="BE18" t="n">
-        <v>-9.31</v>
+        <v>-9</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-145.11</t>
+          <t>-143.60</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>575989895.6908078</t>
+          <t>574936848.40625</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>248447125.0</t>
+          <t>164123235.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>436705282.8</v>
+        <v>446654122.6</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>260191831.6</t>
+          <t>271212851.0</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>369818291.8</v>
+        <v>366042163</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>176513451</t>
+          <t>175441271</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-5262033.339254583</t>
+          <t>-1657380.342235701</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>34738070.37740213</t>
+          <t>18168211.14136815</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>248447125.0</t>
+          <t>164123235.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-15.95</t>
+          <t>-16.47</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,17 +9115,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>251.0</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>243.5</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>245.0</t>
+          <t>243.5</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1323.408</t>
+          <t>1014.014</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>245.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>65.89</t>
+          <t>67.84</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-18.74</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-2.94</v>
+        <v>-2.35</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-10.64</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>251.4</t>
+          <t>250.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>248.5</v>
+        <v>248.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>278.64</v>
+        <v>277.99</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>278.59</t>
+          <t>278.21</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-7.81</v>
+        <v>-7.76</v>
       </c>
       <c r="BE19" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.31</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-146.99</t>
+          <t>-145.11</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>575989895.6908078</t>
+          <t>574936848.40625</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>323015688.0</t>
+          <t>248447125.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>402686874.8</v>
+        <v>436705282.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>242745668.3</t>
+          <t>260191831.6</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>368770174.72</v>
+        <v>369818291.8</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>159941206</t>
+          <t>176513451</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-12534779.4695558</t>
+          <t>-5262033.339254583</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>48133949.98682916</t>
+          <t>34738070.37740213</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>323015688.0</t>
+          <t>248447125.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-16.30</t>
+          <t>-15.95</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>247.5</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>239.5</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>245.0</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4009.203</t>
+          <t>1323.408</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>252.5</t>
+          <t>244.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9739,17 +9739,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>62.71</t>
+          <t>65.89</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-16.25</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,17 +9910,17 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
@@ -9929,47 +9929,47 @@
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>0.12</v>
+        <v>-2.94</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>252.2</t>
+          <t>251.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>249.62</v>
+        <v>248.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>279.32</v>
+        <v>278.64</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>279.14</t>
+          <t>278.59</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>24.58</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-7.67</v>
+        <v>-7.81</v>
       </c>
       <c r="BE20" t="n">
-        <v>-10.17</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-149.27</t>
+          <t>-146.99</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>575989895.6908078</t>
+          <t>574936848.40625</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>1027531470.0</t>
+          <t>323015688.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>354915867.8</v>
+        <v>402686874.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>218126342.9</t>
+          <t>242745668.3</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>369164992.96</v>
+        <v>368770174.72</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>136789524</t>
+          <t>159941206</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-23565457.55253489</t>
+          <t>-12534779.4695558</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>57562362.32219529</t>
+          <t>48133949.98682916</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>1027531470.0</t>
+          <t>323015688.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-16.30</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,17 +10089,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>247.5</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>239.5</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>252.5</t>
+          <t>244.0</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1751.144</t>
+          <t>4009.203</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>268.5</t>
+          <t>252.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>62.71</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-10.95</t>
+          <t>-16.25</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>6.93</v>
+        <v>0.12</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.13</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-10.39</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>252.2</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>250.78</v>
+        <v>249.62</v>
       </c>
       <c r="BA21" t="n">
-        <v>279.86</v>
+        <v>279.32</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>279.58</t>
+          <t>279.14</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>24.58</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-8.24</v>
+        <v>-7.67</v>
       </c>
       <c r="BE21" t="n">
-        <v>-10.79</v>
+        <v>-10.17</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-152.30</t>
+          <t>-149.27</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>575989895.6908078</t>
+          <t>574936848.40625</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>470153095.0</t>
+          <t>1027531470.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>175042945.4</v>
+        <v>354915867.8</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>126184300.1</t>
+          <t>218126342.9</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>356565592.34</v>
+        <v>369164992.96</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>48858645</t>
+          <t>136789524</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-38315970.25703128</t>
+          <t>-23565457.55253489</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-6508109.638788581</t>
+          <t>57562362.32219529</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>470153095.0</t>
+          <t>1027531470.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,17 +10576,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>268.5</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>268.5</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>267.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>268.5</t>
+          <t>252.5</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10678,22 +10678,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>價_量;【b1】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>464.926</t>
+          <t>15713.697</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>244.5</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,22 +10713,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>61.12</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -10738,72 +10738,72 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-07 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2025-09-10 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2025-09-19 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>307.5</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>301.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>317.5</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-18.91</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025/10/01</t>
+          <t>2025/06/03</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>278.0</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -10813,67 +10813,67 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/06/24</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>251.0</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025/10/14</t>
+          <t>2025/03/12</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>284.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2025/11/07</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>301.5</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/03</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-10-29 00:00:00</t>
+          <t>2025-10-23 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,151 +10884,151 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-1.05</v>
+        <v>3.94</v>
       </c>
       <c r="AV22" t="n">
-        <v>-1.76</v>
+        <v>4.22</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-10.1</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>247.1</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>251.52</v>
+        <v>24.32</v>
       </c>
       <c r="BA22" t="n">
-        <v>279.78</v>
+        <v>23.37</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>279.74</t>
+          <t>21.93</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>8.41</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-10.47</v>
+        <v>0.79</v>
       </c>
       <c r="BE22" t="n">
-        <v>-11.43</v>
+        <v>0.64</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-155.39</t>
+          <t>-83.90</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2025/12/04</t>
+          <t>2025/12/23</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>575989895.6908078</t>
+          <t>311411052.4708333</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>114379036.0</t>
+          <t>417370758.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>95771579.40000001</v>
+        <v>311219434</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>89450340.8</t>
+          <t>193165195.8</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>351437032.8</v>
+        <v>185912044.44</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>6321238</t>
+          <t>118054238</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-44099217.64216632</t>
+          <t>10932915.03978593</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-38085811.20309456</t>
+          <t>42189618.67341042</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>114379036.0</t>
+          <t>417370758.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>291.5</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2025/10/20</t>
+          <t>2025/08/14</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>華擎</t>
+          <t>映泰</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
         <is>
-          <t>華擎</t>
+          <t>映泰</t>
         </is>
       </c>
       <c r="BX22" t="inlineStr">
@@ -11043,82 +11043,82 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
         <is>
-          <t>-26.86876387135273</t>
+          <t>-46.22613014733027</t>
         </is>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>21.34391693134842</t>
+          <t>-35.12640290216529</t>
         </is>
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>93.90171918997666</t>
+          <t>-15.51380469022265</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
         <is>
-          <t>94.25</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>13.06%</t>
+          <t>6.53%</t>
         </is>
       </c>
       <c r="CK22" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>-7.23%</t>
         </is>
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>31074</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
         <is>
-          <t>電腦周邊產品94.10%、其他5.90% (2024年)</t>
+          <t>主機板55.98%、其他23.15%、顯示卡11.40%、工業電腦(IPC)9.47% (2024年)</t>
         </is>
       </c>
       <c r="CO22" t="inlineStr">
         <is>
-          <t>華擎-電腦及週邊設備業-上市</t>
+          <t>映泰-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CP22" t="inlineStr">
@@ -11128,32 +11128,32 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>244.5</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
         <is>
-          <t>79.39</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="CV22" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 主機板、顯示卡、工業電腦、伺服器** 區塊鏈 - 元件裝置</t>
+          <t>** 電腦及週邊設備 - 主機板** 區塊鏈 - 元件裝置</t>
         </is>
       </c>
       <c r="CW22" t="inlineStr">
@@ -11165,22 +11165,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>315.713</t>
+          <t>12375.744</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>247.5</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,22 +11200,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-12.98</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -11225,72 +11225,72 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-07 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2025-09-10 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2025-09-19 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>307.5</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>301.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>317.5</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-17.91</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025/10/01</t>
+          <t>2025/06/03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>278.0</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -11300,67 +11300,67 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/06/24</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>251.0</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025/10/14</t>
+          <t>2025/03/12</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>284.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2025/11/07</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>301.5</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/03</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-10-29 00:00:00</t>
+          <t>2025-10-23 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,151 +11371,151 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-0.4</v>
+        <v>4.33</v>
       </c>
       <c r="AV23" t="n">
-        <v>-1.95</v>
+        <v>3.28</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-9.58</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>248.5</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>253.45</v>
+        <v>24.13</v>
       </c>
       <c r="BA23" t="n">
-        <v>280.29</v>
+        <v>23.26</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>280.22</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-10.72</v>
+        <v>0.71</v>
       </c>
       <c r="BE23" t="n">
-        <v>-11.67</v>
+        <v>0.6</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-156.56</t>
+          <t>-84.85</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2025/12/04</t>
+          <t>2025/12/23</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>575989895.6908078</t>
+          <t>311411052.4708333</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>78355085.0</t>
+          <t>319094833.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>83678380.40000001</v>
+        <v>239941531.6</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>96162091.0</t>
+          <t>167711983.3</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>354054785.4</v>
+        <v>179392422.98</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-12483710</t>
+          <t>72229548</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-45192564.26745209</t>
+          <t>5249878.015490573</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-43717956.71627827</t>
+          <t>31668649.45467967</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>78355085.0</t>
+          <t>319094833.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>291.5</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2025/10/20</t>
+          <t>2025/08/14</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-15.09</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>華擎</t>
+          <t>映泰</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
         <is>
-          <t>華擎</t>
+          <t>映泰</t>
         </is>
       </c>
       <c r="BX23" t="inlineStr">
@@ -11530,82 +11530,82 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
         <is>
-          <t>-26.86876387135273</t>
+          <t>-46.22613014733027</t>
         </is>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>21.34391693134842</t>
+          <t>-35.12640290216529</t>
         </is>
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>93.90171918997666</t>
+          <t>-15.51380469022265</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
         <is>
-          <t>94.25</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>13.06%</t>
+          <t>6.53%</t>
         </is>
       </c>
       <c r="CK23" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>-7.23%</t>
         </is>
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>31074</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
-          <t>電腦周邊產品94.10%、其他5.90% (2024年)</t>
+          <t>主機板55.98%、其他23.15%、顯示卡11.40%、工業電腦(IPC)9.47% (2024年)</t>
         </is>
       </c>
       <c r="CO23" t="inlineStr">
         <is>
-          <t>華擎-電腦及週邊設備業-上市</t>
+          <t>映泰-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CP23" t="inlineStr">
@@ -11615,32 +11615,32 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>251.0</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>247.5</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
         <is>
-          <t>79.39</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="CV23" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 主機板、顯示卡、工業電腦、伺服器** 區塊鏈 - 元件裝置</t>
+          <t>** 電腦及週邊設備 - 主機板** 區塊鏈 - 元件裝置</t>
         </is>
       </c>
       <c r="CW23" t="inlineStr">
@@ -11652,7 +11652,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>22853</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>310739915.5884401</t>
+          <t>311411052.4708333</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="CW24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -12174,12 +12174,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>22853</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>310739915.5884401</t>
+          <t>311411052.4708333</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="CW25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -12661,12 +12661,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>22853</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>310739915.5884401</t>
+          <t>311411052.4708333</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="CW26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>22853</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>310739915.5884401</t>
+          <t>311411052.4708333</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="CW27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -13635,12 +13635,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>22853</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>310739915.5884401</t>
+          <t>311411052.4708333</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="CW28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -14122,12 +14122,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -14293,12 +14293,12 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>22853</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>310739915.5884401</t>
+          <t>311411052.4708333</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="CN29" t="inlineStr">
@@ -14567,7 +14567,7 @@
       </c>
       <c r="CW29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -14609,12 +14609,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -14780,12 +14780,12 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>22853</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>310739915.5884401</t>
+          <t>311411052.4708333</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
@@ -14999,12 +14999,12 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="CN30" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="CW30" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -15096,12 +15096,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -15267,12 +15267,12 @@
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>22853</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>310739915.5884401</t>
+          <t>311411052.4708333</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
@@ -15486,12 +15486,12 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="CN31" t="inlineStr">
@@ -15541,1468 +15541,7 @@
       </c>
       <c r="CW31" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>【b1】</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2399</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>6477.899</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>25.4</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>24.93</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2025-12-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2025-12-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2025-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>11.65</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>8.33</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
           <t>False</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>19.15</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>2025/03/12</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>2025/12/19</t>
-        </is>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>22.7</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>15.59</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>22853</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AT32" t="inlineStr">
-        <is>
-          <t>95.45</t>
-        </is>
-      </c>
-      <c r="AU32" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>6.19</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>24.96</t>
-        </is>
-      </c>
-      <c r="AZ32" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>22.51</v>
-      </c>
-      <c r="BB32" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
-      <c r="BC32" t="inlineStr">
-        <is>
-          <t>77.94</t>
-        </is>
-      </c>
-      <c r="BD32" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="BF32" t="inlineStr">
-        <is>
-          <t>3.99</t>
-        </is>
-      </c>
-      <c r="BG32" t="inlineStr">
-        <is>
-          <t>-89.62</t>
-        </is>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2025/12/23</t>
-        </is>
-      </c>
-      <c r="BI32" t="inlineStr">
-        <is>
-          <t>310739915.5884401</t>
-        </is>
-      </c>
-      <c r="BJ32" t="inlineStr">
-        <is>
-          <t>162838633.0</t>
-        </is>
-      </c>
-      <c r="BK32" t="n">
-        <v>210361737.4</v>
-      </c>
-      <c r="BL32" t="inlineStr">
-        <is>
-          <t>168379980.0</t>
-        </is>
-      </c>
-      <c r="BM32" t="n">
-        <v>183024813.82</v>
-      </c>
-      <c r="BN32" t="inlineStr">
-        <is>
-          <t>41981757</t>
-        </is>
-      </c>
-      <c r="BO32" t="inlineStr">
-        <is>
-          <t>4403635.619683392</t>
-        </is>
-      </c>
-      <c r="BP32" t="inlineStr">
-        <is>
-          <t>12014701.01549765</t>
-        </is>
-      </c>
-      <c r="BQ32" t="inlineStr">
-        <is>
-          <t>162838633.0</t>
-        </is>
-      </c>
-      <c r="BR32" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="BS32" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="BT32" t="inlineStr">
-        <is>
-          <t>2025/08/14</t>
-        </is>
-      </c>
-      <c r="BU32" t="inlineStr">
-        <is>
-          <t>32.98</t>
-        </is>
-      </c>
-      <c r="BV32" t="inlineStr">
-        <is>
-          <t>映泰</t>
-        </is>
-      </c>
-      <c r="BW32" t="inlineStr">
-        <is>
-          <t>映泰</t>
-        </is>
-      </c>
-      <c r="BX32" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BY32" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ32" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="CA32" t="inlineStr">
-        <is>
-          <t>-46.22613014733027</t>
-        </is>
-      </c>
-      <c r="CB32" t="inlineStr">
-        <is>
-          <t>-35.12640290216529</t>
-        </is>
-      </c>
-      <c r="CC32" t="inlineStr">
-        <is>
-          <t>-15.51380469022265</t>
-        </is>
-      </c>
-      <c r="CD32" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE32" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CF32" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="CG32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CH32" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="CI32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ32" t="inlineStr">
-        <is>
-          <t>6.53%</t>
-        </is>
-      </c>
-      <c r="CK32" t="inlineStr">
-        <is>
-          <t>-7.23%</t>
-        </is>
-      </c>
-      <c r="CL32" t="inlineStr">
-        <is>
-          <t>27.42</t>
-        </is>
-      </c>
-      <c r="CM32" t="inlineStr">
-        <is>
-          <t>4631</t>
-        </is>
-      </c>
-      <c r="CN32" t="inlineStr">
-        <is>
-          <t>主機板55.98%、其他23.15%、顯示卡11.40%、工業電腦(IPC)9.47% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO32" t="inlineStr">
-        <is>
-          <t>映泰-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CP32" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右上上市</t>
-        </is>
-      </c>
-      <c r="CQ32" t="inlineStr">
-        <is>
-          <t>24.95</t>
-        </is>
-      </c>
-      <c r="CR32" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="CS32" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="CT32" t="inlineStr">
-        <is>
-          <t>25.4</t>
-        </is>
-      </c>
-      <c r="CU32" t="inlineStr">
-        <is>
-          <t>12.09</t>
-        </is>
-      </c>
-      <c r="CV32" t="inlineStr">
-        <is>
-          <t>** 電腦及週邊設備 - 主機板** 區塊鏈 - 元件裝置</t>
-        </is>
-      </c>
-      <c r="CW32" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>【b1】</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2399</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>4348.184</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>24.65</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>5.19</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>63.22</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2025-12-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2025-12-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2025-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>8.35</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>8.33</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>19.15</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>2025/03/12</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>2025/12/19</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>22.7</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>10.46</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>-1.40</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>22853</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>87.88</t>
-        </is>
-      </c>
-      <c r="AT33" t="inlineStr">
-        <is>
-          <t>91.92</t>
-        </is>
-      </c>
-      <c r="AU33" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>5.95</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>24.69</t>
-        </is>
-      </c>
-      <c r="AZ33" t="n">
-        <v>22.74</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>22.38</v>
-      </c>
-      <c r="BB33" t="inlineStr">
-        <is>
-          <t>21.12</t>
-        </is>
-      </c>
-      <c r="BC33" t="inlineStr">
-        <is>
-          <t>92.45</t>
-        </is>
-      </c>
-      <c r="BD33" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BF33" t="inlineStr">
-        <is>
-          <t>3.99</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
-        <is>
-          <t>-91.65</t>
-        </is>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2025/12/23</t>
-        </is>
-      </c>
-      <c r="BI33" t="inlineStr">
-        <is>
-          <t>310739915.5884401</t>
-        </is>
-      </c>
-      <c r="BJ33" t="inlineStr">
-        <is>
-          <t>107832026.0</t>
-        </is>
-      </c>
-      <c r="BK33" t="n">
-        <v>258172989</v>
-      </c>
-      <c r="BL33" t="inlineStr">
-        <is>
-          <t>158179098.5</t>
-        </is>
-      </c>
-      <c r="BM33" t="n">
-        <v>180135902.32</v>
-      </c>
-      <c r="BN33" t="inlineStr">
-        <is>
-          <t>99993890</t>
-        </is>
-      </c>
-      <c r="BO33" t="inlineStr">
-        <is>
-          <t>3019805.547717163</t>
-        </is>
-      </c>
-      <c r="BP33" t="inlineStr">
-        <is>
-          <t>14918621.96306118</t>
-        </is>
-      </c>
-      <c r="BQ33" t="inlineStr">
-        <is>
-          <t>107832026.0</t>
-        </is>
-      </c>
-      <c r="BR33" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="BS33" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="BT33" t="inlineStr">
-        <is>
-          <t>2025/08/14</t>
-        </is>
-      </c>
-      <c r="BU33" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="BV33" t="inlineStr">
-        <is>
-          <t>映泰</t>
-        </is>
-      </c>
-      <c r="BW33" t="inlineStr">
-        <is>
-          <t>映泰</t>
-        </is>
-      </c>
-      <c r="BX33" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BY33" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ33" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="CA33" t="inlineStr">
-        <is>
-          <t>-46.22613014733027</t>
-        </is>
-      </c>
-      <c r="CB33" t="inlineStr">
-        <is>
-          <t>-35.12640290216529</t>
-        </is>
-      </c>
-      <c r="CC33" t="inlineStr">
-        <is>
-          <t>-15.51380469022265</t>
-        </is>
-      </c>
-      <c r="CD33" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE33" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF33" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="CG33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CH33" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="CI33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ33" t="inlineStr">
-        <is>
-          <t>6.53%</t>
-        </is>
-      </c>
-      <c r="CK33" t="inlineStr">
-        <is>
-          <t>-7.23%</t>
-        </is>
-      </c>
-      <c r="CL33" t="inlineStr">
-        <is>
-          <t>27.42</t>
-        </is>
-      </c>
-      <c r="CM33" t="inlineStr">
-        <is>
-          <t>4631</t>
-        </is>
-      </c>
-      <c r="CN33" t="inlineStr">
-        <is>
-          <t>主機板55.98%、其他23.15%、顯示卡11.40%、工業電腦(IPC)9.47% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO33" t="inlineStr">
-        <is>
-          <t>映泰-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CP33" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右上上市</t>
-        </is>
-      </c>
-      <c r="CQ33" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="CR33" t="inlineStr">
-        <is>
-          <t>25.3</t>
-        </is>
-      </c>
-      <c r="CS33" t="inlineStr">
-        <is>
-          <t>24.35</t>
-        </is>
-      </c>
-      <c r="CT33" t="inlineStr">
-        <is>
-          <t>24.65</t>
-        </is>
-      </c>
-      <c r="CU33" t="inlineStr">
-        <is>
-          <t>12.09</t>
-        </is>
-      </c>
-      <c r="CV33" t="inlineStr">
-        <is>
-          <t>** 電腦及週邊設備 - 主機板** 區塊鏈 - 元件裝置</t>
-        </is>
-      </c>
-      <c r="CW33" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>【b1】</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2399</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>10510.954</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>66.27</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2025-12-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2025-12-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2025-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>9.89</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>8.33</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>19.15</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>2025/03/12</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>2025/12/19</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>22.7</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>25.30</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>22853</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>98.48</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>95.96</t>
-        </is>
-      </c>
-      <c r="AU34" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>5.79</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>24.31</t>
-        </is>
-      </c>
-      <c r="AZ34" t="n">
-        <v>22.67</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>22.27</v>
-      </c>
-      <c r="BB34" t="inlineStr">
-        <is>
-          <t>21.05</t>
-        </is>
-      </c>
-      <c r="BC34" t="inlineStr">
-        <is>
-          <t>129.08</t>
-        </is>
-      </c>
-      <c r="BD34" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>3.99</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>-93.58</t>
-        </is>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2025/12/23</t>
-        </is>
-      </c>
-      <c r="BI34" t="inlineStr">
-        <is>
-          <t>310739915.5884401</t>
-        </is>
-      </c>
-      <c r="BJ34" t="inlineStr">
-        <is>
-          <t>264218593.0</t>
-        </is>
-      </c>
-      <c r="BK34" t="n">
-        <v>257686120</v>
-      </c>
-      <c r="BL34" t="inlineStr">
-        <is>
-          <t>154979404.4</t>
-        </is>
-      </c>
-      <c r="BM34" t="n">
-        <v>178334415.42</v>
-      </c>
-      <c r="BN34" t="inlineStr">
-        <is>
-          <t>102706715</t>
-        </is>
-      </c>
-      <c r="BO34" t="inlineStr">
-        <is>
-          <t>856384.3812909778</t>
-        </is>
-      </c>
-      <c r="BP34" t="inlineStr">
-        <is>
-          <t>24427837.56804255</t>
-        </is>
-      </c>
-      <c r="BQ34" t="inlineStr">
-        <is>
-          <t>264218593.0</t>
-        </is>
-      </c>
-      <c r="BR34" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="BS34" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="BT34" t="inlineStr">
-        <is>
-          <t>2025/08/14</t>
-        </is>
-      </c>
-      <c r="BU34" t="inlineStr">
-        <is>
-          <t>30.89</t>
-        </is>
-      </c>
-      <c r="BV34" t="inlineStr">
-        <is>
-          <t>映泰</t>
-        </is>
-      </c>
-      <c r="BW34" t="inlineStr">
-        <is>
-          <t>映泰</t>
-        </is>
-      </c>
-      <c r="BX34" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BY34" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ34" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="CA34" t="inlineStr">
-        <is>
-          <t>-46.22613014733027</t>
-        </is>
-      </c>
-      <c r="CB34" t="inlineStr">
-        <is>
-          <t>-35.12640290216529</t>
-        </is>
-      </c>
-      <c r="CC34" t="inlineStr">
-        <is>
-          <t>-15.51380469022265</t>
-        </is>
-      </c>
-      <c r="CD34" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE34" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF34" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="CG34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CH34" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="CI34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ34" t="inlineStr">
-        <is>
-          <t>6.53%</t>
-        </is>
-      </c>
-      <c r="CK34" t="inlineStr">
-        <is>
-          <t>-7.23%</t>
-        </is>
-      </c>
-      <c r="CL34" t="inlineStr">
-        <is>
-          <t>27.42</t>
-        </is>
-      </c>
-      <c r="CM34" t="inlineStr">
-        <is>
-          <t>4631</t>
-        </is>
-      </c>
-      <c r="CN34" t="inlineStr">
-        <is>
-          <t>主機板55.98%、其他23.15%、顯示卡11.40%、工業電腦(IPC)9.47% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO34" t="inlineStr">
-        <is>
-          <t>映泰-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CP34" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右上上市</t>
-        </is>
-      </c>
-      <c r="CQ34" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="CR34" t="inlineStr">
-        <is>
-          <t>25.65</t>
-        </is>
-      </c>
-      <c r="CS34" t="inlineStr">
-        <is>
-          <t>24.2</t>
-        </is>
-      </c>
-      <c r="CT34" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="CU34" t="inlineStr">
-        <is>
-          <t>12.09</t>
-        </is>
-      </c>
-      <c r="CV34" t="inlineStr">
-        <is>
-          <t>** 電腦及週邊設備 - 主機板** 區塊鏈 - 元件裝置</t>
-        </is>
-      </c>
-      <c r="CW34" t="inlineStr">
-        <is>
-          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/元件裝置.xlsx
+++ b/Result/checksun_type/元件裝置.xlsx
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【d1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>55.98</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-18.29</t>
+          <t>-20.12</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,61 +1149,61 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>82.93</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>78.86</t>
+          <t>68.29</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.54</v>
+        <v>-1.86</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>66.64</t>
+          <t>66.74000000000001</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>65.34</v>
+        <v>65.36</v>
       </c>
       <c r="BA2" t="n">
-        <v>68.3</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>73.69</t>
+          <t>73.51</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>55.22</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="BD2" t="n">
         <v>-0.45</v>
       </c>
       <c r="BE2" t="n">
-        <v>-1</v>
+        <v>-0.89</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-136.89</t>
+          <t>-132.82</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>92016.99897540984</t>
+          <t>91872.18711656441</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>12331.0</t>
+          <t>14136.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>33569.2</v>
+        <v>30540.2</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>21521.3</t>
+          <t>22366.6</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>21547.54</v>
+        <v>21114.9</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>1009.51806638331</t>
+          <t>1093.082305417786</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>2554.570860771906</t>
+          <t>1552.685620107401</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>12331.0</t>
+          <t>14136.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>335.0</t>
+          <t>327.5</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>67.6</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>229.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>60.29</t>
+          <t>55.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-18.66</t>
+          <t>-18.29</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,61 +1636,61 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>75.61</t>
+          <t>82.93</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>84.55</t>
+          <t>78.86</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.12</v>
+        <v>0.54</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>65.96000000000001</t>
+          <t>66.64</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>65.28</v>
+        <v>65.34</v>
       </c>
       <c r="BA3" t="n">
-        <v>68.61</v>
+        <v>68.3</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>73.82</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>47.86</t>
+          <t>55.22</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.59</v>
+        <v>-0.45</v>
       </c>
       <c r="BE3" t="n">
-        <v>-1.13</v>
+        <v>-1</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-141.98</t>
+          <t>-136.89</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>92016.99897540984</t>
+          <t>91872.18711656441</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>15305.0</t>
+          <t>12331.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>33947.6</v>
+        <v>33569.2</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>21178.7</t>
+          <t>21521.3</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>22536.18</v>
+        <v>21547.54</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>728.5993764944743</t>
+          <t>1009.51806638331</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>4087.993673836489</t>
+          <t>2554.570860771906</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>15305.0</t>
+          <t>12331.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>335.0</t>
+          <t>327.5</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.6</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>766.0</t>
+          <t>229.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>64.07</t>
+          <t>60.29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-18.54</t>
+          <t>-18.66</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,61 +2123,61 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>78.05</t>
+          <t>75.61</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>79.64</t>
+          <t>84.55</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1.86</v>
+        <v>1.12</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.49</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>65.96000000000001</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>65.26000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="BA4" t="n">
-        <v>68.90000000000001</v>
+        <v>68.61</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>73.97</t>
+          <t>73.82</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>41.93</t>
+          <t>47.86</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.74</v>
+        <v>-0.59</v>
       </c>
       <c r="BE4" t="n">
-        <v>-1.27</v>
+        <v>-1.13</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-147.00</t>
+          <t>-141.98</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>92016.99897540984</t>
+          <t>91872.18711656441</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>52371.0</t>
+          <t>15305.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>33152</v>
+        <v>33947.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>20206.3</t>
+          <t>21178.7</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>23698.84</v>
+        <v>22536.18</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>117.8004133413808</t>
+          <t>728.5993764944743</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>5813.955061291737</t>
+          <t>4087.993673836489</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>52371.0</t>
+          <t>15305.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>335.0</t>
+          <t>327.5</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>861.0</t>
+          <t>766.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>67.7</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>56.17</t>
+          <t>64.07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-17.44</t>
+          <t>-18.54</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,61 +2610,61 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.05</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>79.64</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>3.9</v>
+        <v>1.86</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.18</v>
+        <v>0.49</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>65.16</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>65.28</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="BA5" t="n">
-        <v>69.20999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>73.97</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>34.20</t>
+          <t>41.93</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.92</v>
+        <v>-0.74</v>
       </c>
       <c r="BE5" t="n">
-        <v>-1.4</v>
+        <v>-1.27</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-151.93</t>
+          <t>-147.00</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>92016.99897540984</t>
+          <t>91872.18711656441</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>58558.0</t>
+          <t>52371.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>24369.8</v>
+        <v>33152</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>15604.4</t>
+          <t>20206.3</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>24153.56</v>
+        <v>23698.84</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-917.8640681041386</t>
+          <t>117.8004133413808</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>4100.61579118167</t>
+          <t>5813.955061291737</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>58558.0</t>
+          <t>52371.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>335.0</t>
+          <t>327.5</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>67.7</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>445.0</t>
+          <t>861.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>39.96</t>
+          <t>56.17</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-20.73</t>
+          <t>-17.44</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,61 +3097,61 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>60.87</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>53.62</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.71</v>
+        <v>3.9</v>
       </c>
       <c r="AV6" t="n">
-        <v>-1.13</v>
+        <v>-0.18</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>64.54</t>
+          <t>65.16</t>
         </is>
       </c>
       <c r="AZ6" t="n">
         <v>65.28</v>
       </c>
       <c r="BA6" t="n">
-        <v>69.47</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>74.21</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>34.20</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-1.24</v>
+        <v>-0.92</v>
       </c>
       <c r="BE6" t="n">
-        <v>-1.52</v>
+        <v>-1.4</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-156.37</t>
+          <t>-151.93</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>92016.99897540984</t>
+          <t>91872.18711656441</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>29281.0</t>
+          <t>58558.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>14193</v>
+        <v>24369.8</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>10140.5</t>
+          <t>15604.4</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>23786.4</v>
+        <v>24153.56</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1830.314951610649</t>
+          <t>-917.8640681041386</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>843.6448413393737</t>
+          <t>4100.61579118167</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>29281.0</t>
+          <t>58558.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>335.0</t>
+          <t>327.5</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>223.0</t>
+          <t>445.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>39.96</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-22.44</t>
+          <t>-20.73</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,62 +3584,62 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>60.87</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="AU7" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>-6.04</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>-6.38</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>64.54</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>65.28</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>69.47</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>74.21</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>18.66</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="BE7" t="n">
         <v>-1.52</v>
       </c>
-      <c r="AV7" t="n">
-        <v>-1.15</v>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>-6.37</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>-6.19</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>64.58000000000001</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>65.33</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>69.77</v>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>74.38</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>15.42</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>-1.59</v>
-      </c>
       <c r="BF7" t="inlineStr">
         <is>
           <t>2.7</t>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-159.00</t>
+          <t>-156.37</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>92016.99897540984</t>
+          <t>91872.18711656441</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>14223.0</t>
+          <t>29281.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>9473.4</v>
+        <v>14193</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>8603.8</t>
+          <t>10140.5</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>24008.74</v>
+        <v>23786.4</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-2316.489459419744</t>
+          <t>-1830.314951610649</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-702.479545626029</t>
+          <t>843.6448413393737</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>14223.0</t>
+          <t>29281.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>335.0</t>
+          <t>327.5</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>223.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-20.98</t>
+          <t>-22.44</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,61 +4071,61 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>21.57</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.37</v>
+        <v>-1.52</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.64</v>
+        <v>-1.15</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>65.03999999999999</t>
+          <t>64.58000000000001</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>65.45999999999999</v>
+        <v>65.33</v>
       </c>
       <c r="BA8" t="n">
-        <v>70.14</v>
+        <v>69.77</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>74.57</t>
+          <t>74.38</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>15.42</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-1.32</v>
+        <v>-1.35</v>
       </c>
       <c r="BE8" t="n">
-        <v>-1.65</v>
+        <v>-1.59</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-161.27</t>
+          <t>-159.00</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>92016.99897540984</t>
+          <t>91872.18711656441</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>11327.0</t>
+          <t>14223.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>8409.799999999999</v>
+        <v>9473.4</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>7684.0</t>
+          <t>8603.8</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>24889.04</v>
+        <v>24008.74</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>869</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-2609.945807382238</t>
+          <t>-2316.489459419744</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-1272.782971804245</t>
+          <t>-702.479545626029</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>11327.0</t>
+          <t>14223.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-7.03</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>335.0</t>
+          <t>327.5</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4315,17 +4315,17 @@
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-20.98</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,61 +4558,61 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.55</v>
+        <v>-0.37</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.82</v>
+        <v>-0.64</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>65.06</t>
+          <t>65.03999999999999</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>65.59999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="BA9" t="n">
-        <v>70.48</v>
+        <v>70.14</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>74.67</t>
+          <t>74.57</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.93</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-1.4</v>
+        <v>-1.32</v>
       </c>
       <c r="BE9" t="n">
-        <v>-1.74</v>
+        <v>-1.65</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-164.32</t>
+          <t>-161.27</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>92016.99897540984</t>
+          <t>91872.18711656441</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>8460.0</t>
+          <t>11327.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>7260.6</v>
+        <v>8409.799999999999</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>7307.0</t>
+          <t>7684.0</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>27036.72</v>
+        <v>24889.04</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-46</t>
+          <t>725</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-2853.066322941873</t>
+          <t>-2609.945807382238</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-1731.759903065828</t>
+          <t>-1272.782971804245</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>8460.0</t>
+          <t>11327.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.03</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>335.0</t>
+          <t>327.5</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-21.22</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,61 +5045,61 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>54.39</t>
+          <t>34.37</t>
         </is>
       </c>
       <c r="AU10" t="n">
         <v>-0.55</v>
       </c>
       <c r="AV10" t="n">
-        <v>-1.13</v>
+        <v>-0.82</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>64.96000000000001</t>
+          <t>65.06</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>65.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="BA10" t="n">
-        <v>70.81999999999999</v>
+        <v>70.48</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>74.67</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-1.46</v>
+        <v>-1.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>-1.82</v>
+        <v>-1.74</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-167.45</t>
+          <t>-164.32</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>92016.99897540984</t>
+          <t>91872.18711656441</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>7674.0</t>
+          <t>8460.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>6839</v>
+        <v>7260.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>7600.3</t>
+          <t>7307.0</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>29167.7</v>
+        <v>27036.72</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-761</t>
+          <t>-46</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-3056.94021746479</t>
+          <t>-2853.066322941873</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-2018.414094044312</t>
+          <t>-1731.759903065828</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>7674.0</t>
+          <t>8460.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>335.0</t>
+          <t>327.5</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>554.066</t>
+          <t>2152.594</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>242.5</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>-19.73</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>23.22</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,17 +5527,17 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
@@ -5546,47 +5546,47 @@
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-1.1</v>
+        <v>-0.82</v>
       </c>
       <c r="AV11" t="n">
-        <v>-1.29</v>
+        <v>-1.66</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>245.2</t>
+          <t>244.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>248.4</v>
+        <v>248.12</v>
       </c>
       <c r="BA11" t="n">
-        <v>265.42</v>
+        <v>263.71</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>273.92</t>
+          <t>272.98</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-4.21</v>
+        <v>-4.27</v>
       </c>
       <c r="BE11" t="n">
-        <v>-4.59</v>
+        <v>-4.53</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-127.99</t>
+          <t>-127.59</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>445804653.335041</t>
+          <t>446528545.5613497</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>134296348.0</t>
+          <t>533191968.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>153047671.4</v>
+        <v>245367250.8</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>136770302.7</t>
+          <t>179716675.4</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>279804751.92</v>
+        <v>277870224.82</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>16277368</t>
+          <t>65650575</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-15168631.04964054</t>
+          <t>-10005992.3899526</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-11112685.64053923</t>
+          <t>18388520.23833108</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>134296348.0</t>
+          <t>533191968.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-16.98</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>16.63</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>29960</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
+          <t>256.5</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>257.5</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
+          <t>241.0</t>
+        </is>
+      </c>
+      <c r="CT11" t="inlineStr">
+        <is>
           <t>242.0</t>
-        </is>
-      </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>244.5</t>
-        </is>
-      </c>
-      <c r="CS11" t="inlineStr">
-        <is>
-          <t>240.5</t>
-        </is>
-      </c>
-      <c r="CT11" t="inlineStr">
-        <is>
-          <t>242.5</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>802.893</t>
+          <t>554.066</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>242.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-19.73</t>
+          <t>-19.57</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.59</v>
+        <v>-1.1</v>
       </c>
       <c r="AV12" t="n">
-        <v>-1.12</v>
+        <v>-1.29</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.41</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>245.9</t>
+          <t>245.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>248.68</v>
+        <v>248.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>266.97</v>
+        <v>265.42</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>274.51</t>
+          <t>273.92</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-4.12</v>
+        <v>-4.21</v>
       </c>
       <c r="BE12" t="n">
-        <v>-4.69</v>
+        <v>-4.59</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-128.57</t>
+          <t>-127.99</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>445804653.335041</t>
+          <t>446528545.5613497</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>195469567.0</t>
+          <t>134296348.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>154417809.6</v>
+        <v>153047671.4</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>134444835.6</t>
+          <t>136770302.7</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>296259431.5</v>
+        <v>279804751.92</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>19972974</t>
+          <t>16277368</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-15906075.66947715</t>
+          <t>-15168631.04964054</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-10121567.4089061</t>
+          <t>-11112685.64053923</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>195469567.0</t>
+          <t>134296348.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-16.98</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>16.63</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>29960</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
           <t>244.5</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>247.5</t>
-        </is>
-      </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>240.5</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>242.5</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>934.767</t>
+          <t>802.893</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>244.5</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>14.86</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-18.91</t>
+          <t>-19.73</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,12 +6501,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6516,243 +6516,243 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-1.21</v>
+        <v>-1.59</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.57</v>
+        <v>-1.12</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
+          <t>245.9</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>248.68</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>266.97</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>274.51</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>12.09</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>-128.57</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>446528545.5613497</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>195469567.0</t>
+        </is>
+      </c>
+      <c r="BK13" t="n">
+        <v>154417809.6</v>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>134444835.6</t>
+        </is>
+      </c>
+      <c r="BM13" t="n">
+        <v>296259431.5</v>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>19972974</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>-15906075.66947715</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>-10121567.4089061</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>195469567.0</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>291.5</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>-16.98</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>華擎</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>華擎</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>62.98279491569413</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>75.64022216352188</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>91.17638493000857</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>94.25</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>16.6</t>
+        </is>
+      </c>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>13.06%</t>
+        </is>
+      </c>
+      <c r="CK13" t="inlineStr">
+        <is>
+          <t>5.37%</t>
+        </is>
+      </c>
+      <c r="CL13" t="inlineStr">
+        <is>
+          <t>27.18</t>
+        </is>
+      </c>
+      <c r="CM13" t="inlineStr">
+        <is>
+          <t>29898</t>
+        </is>
+      </c>
+      <c r="CN13" t="inlineStr">
+        <is>
+          <t>電腦周邊產品94.10%、其他5.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO13" t="inlineStr">
+        <is>
+          <t>華擎-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CP13" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上市</t>
+        </is>
+      </c>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>244.5</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
           <t>247.5</t>
         </is>
       </c>
-      <c r="AZ13" t="n">
-        <v>248.92</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>268.12</v>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>274.77</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="BD13" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>-4.83</v>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>-129.44</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>445804653.335041</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>229517448.0</t>
-        </is>
-      </c>
-      <c r="BK13" t="n">
-        <v>134337008</v>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>136822985.9</t>
-        </is>
-      </c>
-      <c r="BM13" t="n">
-        <v>312102624.38</v>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>-2485977</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>-16957804.44412643</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>-14898473.13482642</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>229517448.0</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>291.5</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>-16.12</t>
-        </is>
-      </c>
-      <c r="BV13" t="inlineStr">
-        <is>
-          <t>華擎</t>
-        </is>
-      </c>
-      <c r="BW13" t="inlineStr">
-        <is>
-          <t>華擎</t>
-        </is>
-      </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="CA13" t="inlineStr">
-        <is>
-          <t>62.98279491569413</t>
-        </is>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>75.64022216352188</t>
-        </is>
-      </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>91.17638493000857</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>3.08</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="CH13" t="inlineStr">
-        <is>
-          <t>94.25</t>
-        </is>
-      </c>
-      <c r="CI13" t="inlineStr">
-        <is>
-          <t>16.63</t>
-        </is>
-      </c>
-      <c r="CJ13" t="inlineStr">
-        <is>
-          <t>13.06%</t>
-        </is>
-      </c>
-      <c r="CK13" t="inlineStr">
-        <is>
-          <t>5.37%</t>
-        </is>
-      </c>
-      <c r="CL13" t="inlineStr">
-        <is>
-          <t>27.65</t>
-        </is>
-      </c>
-      <c r="CM13" t="inlineStr">
-        <is>
-          <t>29960</t>
-        </is>
-      </c>
-      <c r="CN13" t="inlineStr">
-        <is>
-          <t>電腦周邊產品94.10%、其他5.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO13" t="inlineStr">
-        <is>
-          <t>華擎-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CP13" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上市</t>
-        </is>
-      </c>
-      <c r="CQ13" t="inlineStr">
-        <is>
-          <t>251.0</t>
-        </is>
-      </c>
-      <c r="CR13" t="inlineStr">
-        <is>
-          <t>252.0</t>
-        </is>
-      </c>
       <c r="CS13" t="inlineStr">
         <is>
           <t>242.0</t>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>244.5</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>540.577</t>
+          <t>934.767</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>244.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-15.46</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-17.41</t>
+          <t>-18.91</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>0.04</v>
+        <v>-1.21</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.09</v>
+        <v>-0.57</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-7.4</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>248.9</t>
+          <t>247.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>249.12</v>
+        <v>248.92</v>
       </c>
       <c r="BA14" t="n">
-        <v>269.04</v>
+        <v>268.12</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>274.97</t>
+          <t>274.77</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>24.63</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-3.81</v>
+        <v>-3.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>-5.06</v>
+        <v>-4.83</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-130.86</t>
+          <t>-129.44</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>445804653.335041</t>
+          <t>446528545.5613497</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>134360923.0</t>
+          <t>229517448.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>109596100.2</v>
+        <v>134337008</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>129644226.8</t>
+          <t>136822985.9</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>309791561</v>
+        <v>312102624.38</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-20048126</t>
+          <t>-2485977</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-17332228.31854461</t>
+          <t>-16957804.44412643</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-24838523.09561166</t>
+          <t>-14898473.13482642</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>134360923.0</t>
+          <t>229517448.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,17 +7167,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>16.63</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>29960</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>251.0</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>251.5</t>
+          <t>252.0</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>245.5</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>244.5</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>288.853</t>
+          <t>540.577</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-13.99</t>
+          <t>-15.46</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-17.74</t>
+          <t>-17.41</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-0.2</v>
+        <v>0.04</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.3</v>
+        <v>-0.09</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-7.67</t>
+          <t>-7.4</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>248.5</t>
+          <t>248.9</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>249.25</v>
+        <v>249.12</v>
       </c>
       <c r="BA15" t="n">
-        <v>269.97</v>
+        <v>269.04</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>275.1</t>
+          <t>274.97</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>24.63</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-4.11</v>
+        <v>-3.81</v>
       </c>
       <c r="BE15" t="n">
-        <v>-5.37</v>
+        <v>-5.06</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-132.76</t>
+          <t>-130.86</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>445804653.335041</t>
+          <t>446528545.5613497</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>71594071.0</t>
+          <t>134360923.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>114066100</v>
+        <v>109596100.2</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>132620458.0</t>
+          <t>129644226.8</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>310294656.08</v>
+        <v>309791561</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-18554358</t>
+          <t>-20048126</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-15967447.44998696</t>
+          <t>-17332228.31854461</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-27956162.39331871</t>
+          <t>-24838523.09561166</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>71594071.0</t>
+          <t>134360923.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-14.92</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>16.63</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>29960</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>249.5</t>
+          <t>251.5</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>574.304</t>
+          <t>288.853</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-19.83</t>
+          <t>-13.99</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-18.41</t>
+          <t>-17.74</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-1.28</v>
+        <v>-0.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.01</v>
+        <v>-0.3</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-7.98</t>
+          <t>-7.67</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>248.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>249.22</v>
+        <v>249.25</v>
       </c>
       <c r="BA16" t="n">
-        <v>270.84</v>
+        <v>269.97</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>275.31</t>
+          <t>275.1</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-4.32</v>
+        <v>-4.11</v>
       </c>
       <c r="BE16" t="n">
-        <v>-5.69</v>
+        <v>-5.37</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-134.68</t>
+          <t>-132.76</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>445804653.335041</t>
+          <t>446528545.5613497</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>141147039.0</t>
+          <t>71594071.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>120492934</v>
+        <v>114066100</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>150305763.4</t>
+          <t>132620458.0</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>311675854.28</v>
+        <v>310294656.08</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-29812829</t>
+          <t>-18554358</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-13787681.09665392</t>
+          <t>-15967447.44998696</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-24686478.5902817</t>
+          <t>-27956162.39331871</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>141147039.0</t>
+          <t>71594071.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>16.63</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>29960</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>249.5</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>243.5</t>
+          <t>245.5</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8243,7 +8243,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>378.979</t>
+          <t>574.304</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-32.06</t>
+          <t>-19.83</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-18.41</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-0.2</v>
+        <v>-1.28</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.45</v>
+        <v>-0.01</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>-7.98</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>250.5</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>249.38</v>
+        <v>249.22</v>
       </c>
       <c r="BA17" t="n">
-        <v>271.65</v>
+        <v>270.84</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>275.49</t>
+          <t>275.31</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-4.33</v>
+        <v>-4.32</v>
       </c>
       <c r="BE17" t="n">
-        <v>-6.03</v>
+        <v>-5.69</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-136.76</t>
+          <t>-134.68</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>445804653.335041</t>
+          <t>446528545.5613497</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>95065559.0</t>
+          <t>141147039.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>114471861.6</v>
+        <v>120492934</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>168492628.3</t>
+          <t>150305763.4</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>311268981.02</v>
+        <v>311675854.28</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-54020766</t>
+          <t>-29812829</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-11806081.55235796</t>
+          <t>-13787681.09665392</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-26585945.49343303</t>
+          <t>-24686478.5902817</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>95065559.0</t>
+          <t>141147039.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>16.63</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>29960</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>253.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>253.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>249.5</t>
+          <t>243.5</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>423.037</t>
+          <t>378.979</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>251.5</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-46.78</t>
+          <t>-32.06</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-16.58</t>
+          <t>-17.08</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,38 +8936,38 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>53.26</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-8.45</t>
+          <t>-8.2</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -8976,26 +8976,26 @@
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>249.45</v>
+        <v>249.38</v>
       </c>
       <c r="BA18" t="n">
-        <v>272.46</v>
+        <v>271.65</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>275.68</t>
+          <t>275.49</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-4.69</v>
+        <v>-4.33</v>
       </c>
       <c r="BE18" t="n">
-        <v>-6.45</v>
+        <v>-6.03</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-139.35</t>
+          <t>-136.76</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>445804653.335041</t>
+          <t>446528545.5613497</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>105812909.0</t>
+          <t>95065559.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>139308963.8</v>
+        <v>114471861.6</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>261739219.4</t>
+          <t>168492628.3</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>313158870.14</v>
+        <v>311268981.02</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-122430255</t>
+          <t>-54020766</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-9118833.563071579</t>
+          <t>-11806081.55235796</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-23412670.15888375</t>
+          <t>-26585945.49343303</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>105812909.0</t>
+          <t>95065559.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-13.72</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>16.63</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>29960</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
+          <t>253.0</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>253.0</t>
+        </is>
+      </c>
+      <c r="CS18" t="inlineStr">
+        <is>
           <t>249.5</t>
         </is>
       </c>
-      <c r="CR18" t="inlineStr">
-        <is>
-          <t>252.5</t>
-        </is>
-      </c>
-      <c r="CS18" t="inlineStr">
-        <is>
-          <t>246.5</t>
-        </is>
-      </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>251.5</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>629.331</t>
+          <t>423.037</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>251.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-49.80</t>
+          <t>-46.78</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-18.08</t>
+          <t>-16.58</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>53.26</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-1.12</v>
+        <v>0.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.13</v>
+        <v>0.42</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-8.45</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>249.8</t>
+          <t>250.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>249.48</v>
+        <v>249.45</v>
       </c>
       <c r="BA19" t="n">
-        <v>273.2</v>
+        <v>272.46</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>276.01</t>
+          <t>275.68</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-5.22</v>
+        <v>-4.69</v>
       </c>
       <c r="BE19" t="n">
-        <v>-6.9</v>
+        <v>-6.45</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-142.04</t>
+          <t>-139.35</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>445804653.335041</t>
+          <t>446528545.5613497</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>156710922.0</t>
+          <t>105812909.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>149692353.4</v>
+        <v>139308963.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>298173238.0</t>
+          <t>261739219.4</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>314265751.62</v>
+        <v>313158870.14</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-148480884</t>
+          <t>-122430255</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-6519954.18201482</t>
+          <t>-9118833.563071579</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-19194754.67528179</t>
+          <t>-23412670.15888375</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>156710922.0</t>
+          <t>105812909.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-13.72</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>16.63</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>29960</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>253.0</t>
+          <t>249.5</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>254.0</t>
+          <t>252.5</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>251.5</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3708.31</t>
+          <t>3441.565</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,159 +9729,159 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-4.25</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-12-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-12-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
           <t>25.85</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-7.60</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-12-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-12-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>24.4</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-4.84</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>7.17</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025/06/03</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>19.15</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2025/03/12</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>25.85</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
         <is>
           <t>24.4</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>7.17</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>19.15</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>2025/03/12</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>2026/01/07</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>25.85</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
       <c r="AK20" t="inlineStr">
         <is>
           <t>2025-10-23 00:00:00</t>
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-1.15</v>
+        <v>-4.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.82</v>
+        <v>2.67</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.84</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>25.19</v>
+        <v>25.17</v>
       </c>
       <c r="BA20" t="n">
-        <v>23.73</v>
+        <v>23.71</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-15.13</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-81.78</t>
+          <t>-82.44</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,48 +9988,48 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>370941356.6127049</t>
+          <t>370447401.1533743</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>96388330.0</t>
+          <t>86264758.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>276914854</v>
+        <v>239081740.6</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>299692456.4</t>
+          <t>249697128.7</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>159416236.94</v>
+        <v>156071980.48</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-22777602</t>
+          <t>-10615388</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>19149029.32792524</t>
+          <t>14977623.79909235</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>3183682.093231767</t>
+          <t>-7965106.609488517</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>96388330.0</t>
+          <t>86264758.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>28.80</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10191,7 +10191,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3932.75</t>
+          <t>3708.31</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-7.60</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,63 +10397,63 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>39.66</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>63.79</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-1.2</v>
+        <v>-1.15</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.9</v>
+        <v>3.82</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>25.13</v>
+        <v>25.19</v>
       </c>
       <c r="BA21" t="n">
         <v>23.73</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BE21" t="n">
         <v>0.73</v>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-81.76</t>
+          <t>-81.78</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>370941356.6127049</t>
+          <t>370447401.1533743</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>101130799.0</t>
+          <t>96388330.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>275283088.4</v>
+        <v>276914854</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>294537776.4</t>
+          <t>299692456.4</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>173008221.5</v>
+        <v>159416236.94</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-19254688</t>
+          <t>-22777602</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>22051819.73423314</t>
+          <t>19149029.32792524</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>17912151.73664531</t>
+          <t>3183682.093231767</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>101130799.0</t>
+          <t>96388330.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -10576,17 +10576,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9908.484</t>
+          <t>3932.75</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,29 +10884,29 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>51.72</t>
+          <t>39.66</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>81.07</t>
+          <t>63.79</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>0.5</v>
+        <v>-1.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
@@ -10915,35 +10915,35 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>25.1</v>
+        <v>25.13</v>
       </c>
       <c r="BA22" t="n">
-        <v>23.71</v>
+        <v>23.73</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-81.91</t>
+          <t>-81.76</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>370941356.6127049</t>
+          <t>370447401.1533743</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>263859626.0</t>
+          <t>101130799.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>295344361.8</v>
+        <v>275283088.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>303281897.9</t>
+          <t>294537776.4</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>191706801.76</v>
+        <v>173008221.5</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-7937536</t>
+          <t>-19254688</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>22804486.64288548</t>
+          <t>22051819.73423314</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>37804981.27235588</t>
+          <t>17912151.73664531</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>263859626.0</t>
+          <t>101130799.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>35.60</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -11063,17 +11063,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23768.28</t>
+          <t>9908.484</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>57.20</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>51.72</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>81.07</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>5.57</v>
+        <v>0.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.39</v>
+        <v>2.65</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>25.01</v>
+        <v>25.1</v>
       </c>
       <c r="BA23" t="n">
-        <v>23.69</v>
+        <v>23.71</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-82.44</t>
+          <t>-81.91</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>370941356.6127049</t>
+          <t>370447401.1533743</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>647765190.0</t>
+          <t>263859626.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>326046588.2</v>
+        <v>295344361.8</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>282994059.9</t>
+          <t>303281897.9</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>197249136.02</v>
+        <v>191706801.76</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>43052528</t>
+          <t>-7937536</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>20077123.98298177</t>
+          <t>22804486.64288548</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>47437899.81364399</t>
+          <t>37804981.27235588</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>647765190.0</t>
+          <t>263859626.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>42.93</t>
+          <t>35.60</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11550,17 +11550,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
@@ -11590,47 +11590,47 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
+          <t>27.18</t>
+        </is>
+      </c>
+      <c r="CM23" t="inlineStr">
+        <is>
+          <t>4381</t>
+        </is>
+      </c>
+      <c r="CN23" t="inlineStr">
+        <is>
+          <t>主機板55.98%、其他23.15%、顯示卡11.40%、工業電腦(IPC)9.47% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO23" t="inlineStr">
+        <is>
+          <t>映泰-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CP23" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上市</t>
+        </is>
+      </c>
+      <c r="CQ23" t="inlineStr">
+        <is>
           <t>27.65</t>
         </is>
       </c>
-      <c r="CM23" t="inlineStr">
-        <is>
-          <t>4604</t>
-        </is>
-      </c>
-      <c r="CN23" t="inlineStr">
-        <is>
-          <t>主機板55.98%、其他23.15%、顯示卡11.40%、工業電腦(IPC)9.47% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO23" t="inlineStr">
-        <is>
-          <t>映泰-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CP23" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上市</t>
-        </is>
-      </c>
-      <c r="CQ23" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10776.951</t>
+          <t>23768.28</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,159 +11677,159 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>27.3</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-10.98</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>15.21</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2025-12-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2025-12-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-1.16</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>17.31</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2025-12-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2025-12-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>25.85</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>24.4</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>5.61</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>7.17</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025/06/03</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>19.15</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>2025/03/12</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
         <is>
           <t>25.85</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
         <is>
           <t>24.4</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>7.17</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>19.15</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>2025/03/12</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>2026/01/07</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>25.85</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
       <c r="AK24" t="inlineStr">
         <is>
           <t>2025-10-23 00:00:00</t>
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>57.20</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,67 +11858,67 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>51.77</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>2.15</v>
+        <v>5.57</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.29</v>
+        <v>3.39</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>24.78</v>
+        <v>25.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>23.59</v>
+        <v>23.69</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>18.24</t>
         </is>
       </c>
       <c r="BD24" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BE24" t="n">
         <v>0.7</v>
       </c>
-      <c r="BE24" t="n">
-        <v>0.67</v>
-      </c>
       <c r="BF24" t="inlineStr">
         <is>
           <t>3.99</t>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-83.24</t>
+          <t>-82.44</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>370941356.6127049</t>
+          <t>370447401.1533743</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>275430325.0</t>
+          <t>647765190.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>260312516.8</v>
+        <v>326046588.2</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>221895918.0</t>
+          <t>282994059.9</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>187761390.98</v>
+        <v>197249136.02</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>38416598</t>
+          <t>43052528</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>15102437.46831591</t>
+          <t>20077123.98298177</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>18372262.30785406</t>
+          <t>47437899.81364399</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>275430325.0</t>
+          <t>647765190.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>42.93</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12037,17 +12037,17 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12139,7 +12139,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3603.533</t>
+          <t>10776.951</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,159 +12164,159 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-6.3</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>17.31</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2025-12-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2025-12-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>25.85</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
           <t>24.4</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>5.61</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>61.49</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2025-12-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2025-12-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>7.17</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025/06/03</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>19.15</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>2025/03/12</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
         <is>
           <t>25.85</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
         <is>
           <t>24.4</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>-6.15</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>-5.61</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>7.17</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>19.15</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>2025/03/12</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>2026/01/07</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>25.85</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
       <c r="AK25" t="inlineStr">
         <is>
           <t>2025-10-23 00:00:00</t>
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,66 +12345,66 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>54.61</t>
+          <t>51.77</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-4.58</v>
+        <v>2.15</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.09</v>
+        <v>3.29</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>24.56</v>
+        <v>24.78</v>
       </c>
       <c r="BA25" t="n">
-        <v>23.5</v>
+        <v>23.59</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-83.45</t>
+          <t>-83.24</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,48 +12423,48 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>370941356.6127049</t>
+          <t>370447401.1533743</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>88229502.0</t>
+          <t>275430325.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>322470058.8</v>
+        <v>260312516.8</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>199686197.6</t>
+          <t>221895918.0</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>183591006.34</v>
+        <v>187761390.98</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>122783861</t>
+          <t>38416598</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>14507923.86112716</t>
+          <t>15102437.46831591</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>16086792.0385879</t>
+          <t>18372262.30785406</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>88229502.0</t>
+          <t>275430325.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12524,17 +12524,17 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12626,7 +12626,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7891.205</t>
+          <t>3603.533</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>61.49</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12731,12 +12731,12 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-6.15</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,38 +12832,38 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>82.27</t>
+          <t>54.61</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-1.84</v>
+        <v>-4.58</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.59</v>
+        <v>4.09</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -12872,23 +12872,23 @@
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>24.45</v>
+        <v>24.56</v>
       </c>
       <c r="BA26" t="n">
-        <v>23.43</v>
+        <v>23.5</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="BE26" t="n">
         <v>0.66</v>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-83.37</t>
+          <t>-83.45</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>370941356.6127049</t>
+          <t>370447401.1533743</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>201437166.0</t>
+          <t>88229502.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>313792464.4</v>
+        <v>322470058.8</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>197650270.6</t>
+          <t>199686197.6</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>183786930.9</v>
+        <v>183591006.34</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>116142193</t>
+          <t>122783861</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>14220856.91977066</t>
+          <t>14507923.86112716</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>32304537.25968668</t>
+          <t>16086792.0385879</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>201437166.0</t>
+          <t>88229502.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>15713.697</t>
+          <t>7891.205</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>61.12</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.27</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>3.94</v>
+        <v>-1.84</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.22</v>
+        <v>4.59</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>24.32</v>
+        <v>24.45</v>
       </c>
       <c r="BA27" t="n">
-        <v>23.37</v>
+        <v>23.43</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-83.90</t>
+          <t>-83.37</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>370941356.6127049</t>
+          <t>370447401.1533743</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>417370758.0</t>
+          <t>201437166.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>311219434</v>
+        <v>313792464.4</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>193165195.8</t>
+          <t>197650270.6</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>185912044.44</v>
+        <v>183786930.9</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>118054238</t>
+          <t>116142193</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>10932915.03978593</t>
+          <t>14220856.91977066</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>42189618.67341042</t>
+          <t>32304537.25968668</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>417370758.0</t>
+          <t>201437166.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>31.41</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>12375.744</t>
+          <t>15713.697</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,177 +13625,177 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>26.35</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-7.11</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>61.12</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2025-12-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2025-12-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>25.85</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
           <t>26.0</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>43.07</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2025-12-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2025-12-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>24.4</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>7.17</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025/06/03</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>19.15</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>2025/03/12</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
         <is>
           <t>25.85</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>24.4</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>7.17</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>37.82</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
         <is>
           <t>0.05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>19.15</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>2025/03/12</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>2026/01/07</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>25.85</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>29.78</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>2.20</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13821,51 +13821,51 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>4.33</v>
+        <v>3.94</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.28</v>
+        <v>4.22</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>24.13</v>
+        <v>24.32</v>
       </c>
       <c r="BA28" t="n">
-        <v>23.26</v>
+        <v>23.37</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.93</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="BE28" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-84.85</t>
+          <t>-83.90</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>370941356.6127049</t>
+          <t>370447401.1533743</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>319094833.0</t>
+          <t>417370758.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>239941531.6</v>
+        <v>311219434</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>167711983.3</t>
+          <t>193165195.8</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>179392422.98</v>
+        <v>185912044.44</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>72229548</t>
+          <t>118054238</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>5249878.015490573</t>
+          <t>10932915.03978593</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>31668649.45467967</t>
+          <t>42189618.67341042</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>319094833.0</t>
+          <t>417370758.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
